--- a/documentation/Copy of Unit_Test_Plan_v0.1.xlsx
+++ b/documentation/Copy of Unit_Test_Plan_v0.1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ba97a91002e3819/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ba97a91002e3819/Documents/AI-Career-companion-Agent/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEB05C55-E6EA-4A52-9861-372D38FAE193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{BEB05C55-E6EA-4A52-9861-372D38FAE193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6D70B8A-ACF9-4B43-89D8-244171801BE3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>Actual Result</t>
   </si>
@@ -229,6 +229,111 @@
   </si>
   <si>
     <t>The workflow executed successfully for the sample resumes and generated relevant results</t>
+  </si>
+  <si>
+    <t>M3 Skill Gap Analysis Agent</t>
+  </si>
+  <si>
+    <t>Select a job and run the skill gap analysis</t>
+  </si>
+  <si>
+    <t>Verify that candidate skills are compared with the selected job requirements</t>
+  </si>
+  <si>
+    <t>The system should identify existing, partial, and missing skills and provide improvement recommendations</t>
+  </si>
+  <si>
+    <t>Skill gaps were identified successfully and personalized improvement recommendations were generated</t>
+  </si>
+  <si>
+    <t>M3 Resume and Cover Letter Customization</t>
+  </si>
+  <si>
+    <t>Select a job and generate customized resume and cover letter content</t>
+  </si>
+  <si>
+    <t>Verify that the generated content is tailored to the selected job using the candidate's actual profile</t>
+  </si>
+  <si>
+    <t>Role-specific resume content and cover letter should be generated without unsupported skills or experience</t>
+  </si>
+  <si>
+    <t>Customized resume content and a job-specific cover letter were generated successfully</t>
+  </si>
+  <si>
+    <t>M3 Interview Preparation Agent</t>
+  </si>
+  <si>
+    <t>Select a job and generate interview preparation</t>
+  </si>
+  <si>
+    <t>Verify that questions are generated based on the selected role, candidate profile, projects, and skill gaps</t>
+  </si>
+  <si>
+    <t>The system should generate technical, resume, project, role-specific, and HR questions with preparation guidance</t>
+  </si>
+  <si>
+    <t>Interview questions, preparation guidance, revision topics, and skill-gap preparation were generated successfully</t>
+  </si>
+  <si>
+    <t>M3 Mock Interview</t>
+  </si>
+  <si>
+    <t>Start a mock interview for the selected job and answer the questions</t>
+  </si>
+  <si>
+    <t>Verify that the system conducts an interactive interview using multiple questions</t>
+  </si>
+  <si>
+    <t>The system should display interview questions sequentially and accept candidate responses</t>
+  </si>
+  <si>
+    <t>Mock interview was conducted successfully with questions presented sequentially and responses recorded</t>
+  </si>
+  <si>
+    <t>M3 Conversational Career Assistant</t>
+  </si>
+  <si>
+    <t>Ask natural-language questions about the selected job, skills, and interview preparation</t>
+  </si>
+  <si>
+    <t>Verify that the career assistant uses candidate profile, selected job, skill gaps, and interview context</t>
+  </si>
+  <si>
+    <t>The system should provide personalized and relevant career guidance</t>
+  </si>
+  <si>
+    <t>Career assistant generated personalized responses using the available candidate and job context</t>
+  </si>
+  <si>
+    <t>M3 Career Assistant Context Retention</t>
+  </si>
+  <si>
+    <t>Ask a follow-up question referring to information discussed previously</t>
+  </si>
+  <si>
+    <t>Verify that the assistant retains recent conversation context</t>
+  </si>
+  <si>
+    <t>The assistant should understand follow-up questions and provide context-aware responses</t>
+  </si>
+  <si>
+    <t>The assistant retained the conversation context and correctly responded to follow-up questions</t>
+  </si>
+  <si>
+    <t>M3 End-to-End Validation</t>
+  </si>
+  <si>
+    <t>Execute the Milestone 3 workflow using a sample candidate and selected job</t>
+  </si>
+  <si>
+    <t>Verify that all M3 agents work together successfully</t>
+  </si>
+  <si>
+    <t>Skill gap, resume/cover letter, interview preparation, mock interview, and career assistant features should work successfully</t>
+  </si>
+  <si>
+    <t>All tested Milestone 3 features executed successfully</t>
   </si>
 </sst>
 </file>
@@ -635,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -905,21 +1010,148 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
+      <c r="B16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="105.6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="92.4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="105.6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="105.6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E21" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/documentation/Copy of Unit_Test_Plan_v0.1.xlsx
+++ b/documentation/Copy of Unit_Test_Plan_v0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ba97a91002e3819/Documents/AI-Career-companion-Agent/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{BEB05C55-E6EA-4A52-9861-372D38FAE193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6D70B8A-ACF9-4B43-89D8-244171801BE3}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{BEB05C55-E6EA-4A52-9861-372D38FAE193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D9D236A-6087-44F4-91C5-9D0AA4042DC1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="134">
   <si>
     <t>Actual Result</t>
   </si>
@@ -334,6 +334,108 @@
   </si>
   <si>
     <t>All tested Milestone 3 features executed successfully</t>
+  </si>
+  <si>
+    <t>Add Application Record</t>
+  </si>
+  <si>
+    <t>Enter valid job or internship details and submit.</t>
+  </si>
+  <si>
+    <t>Verify that a new application can be created</t>
+  </si>
+  <si>
+    <t>The application should be saved and displayed.</t>
+  </si>
+  <si>
+    <t>Record the result after testing.</t>
+  </si>
+  <si>
+    <t>View Saved Applications</t>
+  </si>
+  <si>
+    <t>Open the application tracking page.</t>
+  </si>
+  <si>
+    <t>Verify that saved records are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Saved applications should be displayed correctly.</t>
+  </si>
+  <si>
+    <t>Update Application Status</t>
+  </si>
+  <si>
+    <t>Change the status of an existing application and save it.</t>
+  </si>
+  <si>
+    <t>Verify that the updated status is stored and displayed.</t>
+  </si>
+  <si>
+    <t>The new status should be displayed correctly.</t>
+  </si>
+  <si>
+    <t>Edit Application Detail</t>
+  </si>
+  <si>
+    <t>Modify the details of an existing application.</t>
+  </si>
+  <si>
+    <t>Verify that changes are saved correctly.</t>
+  </si>
+  <si>
+    <t>The updated details should be displayed.</t>
+  </si>
+  <si>
+    <t>Record the result after testing</t>
+  </si>
+  <si>
+    <t>Delete Application Recor</t>
+  </si>
+  <si>
+    <t>Delete an application using the supported interface</t>
+  </si>
+  <si>
+    <t>Verify that the selected record is removed</t>
+  </si>
+  <si>
+    <t>The deleted record should no longer appear.</t>
+  </si>
+  <si>
+    <t>Validate Required Fields</t>
+  </si>
+  <si>
+    <t>Submit an application with required fields missing.</t>
+  </si>
+  <si>
+    <t>Verify input validation.</t>
+  </si>
+  <si>
+    <t>The application should prevent invalid submission or display an appropriate validation message</t>
+  </si>
+  <si>
+    <t>Application Data Persistence</t>
+  </si>
+  <si>
+    <t>Save an application and reopen the tracking page</t>
+  </si>
+  <si>
+    <t>Verify that saved details remain available.</t>
+  </si>
+  <si>
+    <t>The saved record should remain available according to the application's storage design.</t>
+  </si>
+  <si>
+    <t>Application Tracking Integration</t>
+  </si>
+  <si>
+    <t>Open application tracking from the existing application and use its supported features.</t>
+  </si>
+  <si>
+    <t>Verify integration with the existing Flask application.</t>
+  </si>
+  <si>
+    <t>The tracking workflow should work without breaking existing features.</t>
   </si>
 </sst>
 </file>
@@ -740,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -1150,8 +1252,183 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E21" s="4"/>
+    <row r="21" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+    </row>
+    <row r="34" spans="1:1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
